--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260826.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260826.xlsx
@@ -975,17 +975,17 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>13,112,000</t>
+          <t>2,572,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -997,17 +997,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>2,572,000</t>
+          <t>13,112,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>4766</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>和泰車</t>
+          <t>南寶</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>2,330,000</t>
+          <t>3,534,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>4766</t>
+          <t>2207</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>南寶</t>
+          <t>和泰車</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>3,534,000</t>
+          <t>2,330,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>12,795,000</t>
+          <t>2,075,678</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>2,075,678</t>
+          <t>12,795,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>2903</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>國產</t>
+          <t>遠百</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>24,799,000</t>
+          <t>35,227,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2504</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>國產</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>7,825,000</t>
+          <t>24,799,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2903</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>遠百</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>35,227,000</t>
+          <t>7,825,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
